--- a/outputs/figure_source_data/source_data_fig_3_c.xlsx
+++ b/outputs/figure_source_data/source_data_fig_3_c.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -581,9 +581,11 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,10 +631,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>mas_ks_normality_p</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>human_ks_normality_p</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>significance_label</t>
         </is>
@@ -670,13 +682,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0820361281354391</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+        <v>0.0318055868090052</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.1170776379981861</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.3126888966048078</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -714,13 +732,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0820361281354391</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+        <v>0.0318055868090052</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.1170776379981861</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.3126888966048078</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -758,13 +782,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.0349310778936544</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+        <v>0.0007102711089982</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.0021019383337615</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.069308902784467</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -802,13 +832,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.0349310778936544</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+        <v>0.0007102711089982</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.0021019383337615</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.069308902784467</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -846,13 +882,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.3905789907528655</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+        <v>0.4054027898183875</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.2679210138401441</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.971482334935176</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -890,13 +932,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.3905789907528655</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+        <v>0.4054027898183875</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.2679210138401441</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.971482334935176</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -934,13 +982,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.7526295405381827</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+        <v>0.8888875116899874</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.4353376472465687</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.829989643040927</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -978,13 +1032,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.7526295405381827</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+        <v>0.8888875116899874</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.4353376472465687</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.829989643040927</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1022,13 +1082,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.1237741762518294</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+        <v>0.1042371939586176</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.6331469942067196</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.3985718539319581</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1066,13 +1132,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.1237741762518294</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+        <v>0.1042371939586176</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.6331469942067196</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.3985718539319581</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1110,13 +1182,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.0302573512089332</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+        <v>0.0013189464506088</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.0238978310024238</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.0864991061184003</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1154,13 +1232,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Mann-Whitney U test</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.0302573512089332</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+        <v>0.0013189464506088</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.0238978310024238</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.0864991061184003</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1198,13 +1282,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.1934511065220663</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+        <v>0.7168935131728096</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.3154983844850926</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.5940123284756647</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1242,13 +1332,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.1934511065220663</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+        <v>0.7168935131728096</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.3154983844850926</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.5940123284756647</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1286,13 +1382,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.0234063720725031</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+        <v>0.6287126987088119</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.6815505682416169</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.1596464460747123</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1330,13 +1432,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.0234063720725031</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+        <v>0.6287126987088119</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.6815505682416169</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.1596464460747123</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1374,13 +1482,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.4267047223481617</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+        <v>0.0919968461511077</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.2390758271507026</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.7233577537998733</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1418,13 +1532,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.4267047223481617</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+        <v>0.0919968461511077</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.2390758271507026</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.7233577537998733</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1462,13 +1582,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.5785552980043588</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+        <v>0.3938900956195077</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.1704211187240956</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.6136005669688815</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1506,13 +1632,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.5785552980043588</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+        <v>0.3938900956195077</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.1704211187240956</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.6136005669688815</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1550,13 +1682,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.4127390212917594</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+        <v>0.5967264905274794</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.3271355825576195</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.6712732194568269</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1594,13 +1732,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.4127390212917594</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+        <v>0.5967264905274794</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.3271355825576195</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.6712732194568269</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1638,13 +1782,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.0638563387706064</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+        <v>0.8384060206627867</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.92166963215955</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.1842896953370707</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -1682,13 +1832,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.0638563387706064</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+        <v>0.8384060206627867</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.92166963215955</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.1842896953370707</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
